--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -3,40 +3,25 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\budchane\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0D531A-F1FB-41BE-A93C-50B32724AD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{6E67C687-2167-48C6-8886-C1771582A4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" xr2:uid="{2FC947E8-CD84-4325-9107-81AEF1AC1484}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2FC947E8-CD84-4325-9107-81AEF1AC1484}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>FirstName</t>
   </si>
@@ -62,40 +47,13 @@
     <t>Response</t>
   </si>
   <si>
-    <t>8387689</t>
-  </si>
-  <si>
-    <t>https://gorest.co.in/public/v2</t>
+    <t>ff8081819cd4022c019ce6d561782156</t>
   </si>
   <si>
     <t>{
-    "id": 8387689,
+    "id": "ff8081819cd4022c019ce6d561782156",
     "name": "John",
-    "email": "user_1772193115300@example.com",
-    "gender": "male",
-    "status": "active"
-}</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>{
-    "status": 500,
-    "error": "Internal Server Error"
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbc721f6b28a1</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbc77588828b2</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbc77588828b2",
-    "name": "John",
-    "createdAt": 1772688464008,
+    "createdAt": 1773399269752,
     "data": {
         "color": "Cloudy White",
         "name": "John",
@@ -105,141 +63,13 @@
 }</t>
   </si>
   <si>
-    <t>ff8081819c5368bb019cbca5cc122953</t>
+    <t>ff8081819cd4022c019ce6dcbe322163</t>
   </si>
   <si>
     <t>{
-    "id": "ff8081819c5368bb019cbca5cc122953",
+    "id": "ff8081819cd4022c019ce6dcbe322163",
     "name": "John",
-    "createdAt": 1772691508243,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbcacad5f2961</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbcacad5f2961",
-    "name": "John",
-    "createdAt": 1772691959135,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbcb25c422976</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbcb25c422976",
-    "name": "John",
-    "createdAt": 1772692331586,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbcb460c22984</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbcb460c22984",
-    "name": "John",
-    "createdAt": 1772692463810,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbcd127982a2d</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbcd127982a2d",
-    "name": "John",
-    "createdAt": 1772694349720,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbcddca152a47</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbcddca152a47",
-    "name": "John",
-    "createdAt": 1772695177749,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbce1b5602a4f</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbce1b5602a4f",
-    "name": "John",
-    "createdAt": 1772695434592,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbe2c9cb22d32</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbe2c9cb22d32",
-    "name": "John",
-    "createdAt": 1772717120690,
-    "data": {
-        "color": "Cloudy White",
-        "name": "John",
-        "job": "Doe",
-        "capacity": "128 GB"
-    }
-}</t>
-  </si>
-  <si>
-    <t>ff8081819c5368bb019cbe3391d32d4b</t>
-  </si>
-  <si>
-    <t>{
-    "id": "ff8081819c5368bb019cbe3391d32d4b",
-    "name": "John",
-    "createdAt": 1772717576659,
+    "createdAt": 1773399752242,
     "data": {
         "color": "Cloudy White",
         "name": "John",
@@ -324,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -344,44 +174,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
@@ -725,6 +519,9 @@
   <cols>
     <col min="1" max="1" customWidth="true" width="14.1796875"/>
     <col min="2" max="2" customWidth="true" width="16.26953125"/>
+    <col min="3" max="3" customWidth="true" width="18.81640625"/>
+    <col min="4" max="4" customWidth="true" width="12.7265625"/>
+    <col min="5" max="5" customWidth="true" width="22.08984375"/>
     <col min="6" max="6" customWidth="true" width="15.81640625"/>
   </cols>
   <sheetData>
@@ -747,7 +544,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -755,13 +552,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>200.0</v>
       </c>
-      <c r="E2" t="s" s="22">
-        <v>33</v>
+      <c r="E2" t="s" s="10">
+        <v>11</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="7"/>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>FirstName</t>
   </si>
@@ -70,6 +70,38 @@
     "id": "ff8081819cd4022c019ce6dcbe322163",
     "name": "John",
     "createdAt": 1773399752242,
+    "data": {
+        "color": "Cloudy White",
+        "name": "John",
+        "job": "Doe",
+        "capacity": "128 GB"
+    }
+}</t>
+  </si>
+  <si>
+    <t>ff8081819cd4022c019cff8acc5c4366</t>
+  </si>
+  <si>
+    <t>{
+    "id": "ff8081819cd4022c019cff8acc5c4366",
+    "name": "John",
+    "createdAt": 1773813812316,
+    "data": {
+        "color": "Cloudy White",
+        "name": "John",
+        "job": "Doe",
+        "capacity": "128 GB"
+    }
+}</t>
+  </si>
+  <si>
+    <t>ff8081819cd4022c019d09f2e5df5451</t>
+  </si>
+  <si>
+    <t>{
+    "id": "ff8081819cd4022c019d09f2e5df5451",
+    "name": "John",
+    "createdAt": 1773988406751,
     "data": {
         "color": "Cloudy White",
         "name": "John",
@@ -154,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -176,6 +208,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
@@ -552,13 +590,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>200.0</v>
       </c>
-      <c r="E2" t="s" s="10">
-        <v>11</v>
+      <c r="E2" t="s" s="12">
+        <v>15</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="7"/>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>FirstName</t>
   </si>
@@ -102,6 +102,22 @@
     "id": "ff8081819cd4022c019d09f2e5df5451",
     "name": "John",
     "createdAt": 1773988406751,
+    "data": {
+        "color": "Cloudy White",
+        "name": "John",
+        "job": "Doe",
+        "capacity": "128 GB"
+    }
+}</t>
+  </si>
+  <si>
+    <t>ff8081819d150699019d19bf10ec064b</t>
+  </si>
+  <si>
+    <t>{
+    "id": "ff8081819d150699019d19bf10ec064b",
+    "name": "John",
+    "createdAt": 1774253445356,
     "data": {
         "color": "Cloudy White",
         "name": "John",
@@ -186,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -208,6 +224,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
@@ -590,13 +609,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>200.0</v>
       </c>
-      <c r="E2" t="s" s="12">
-        <v>15</v>
+      <c r="E2" t="s" s="13">
+        <v>17</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="7"/>
